--- a/yudao-module-reagent/src/main/resources/templates/reagent-label-print.xlsx
+++ b/yudao-module-reagent/src/main/resources/templates/reagent-label-print.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="试剂标签" r:id="rId3" sheetId="1"/>
+    <sheet name="Reagent Label" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -29,10 +29,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
-    <t>试剂标签</t>
-  </si>
-  <si>
-    <t>名称:</t>
+    <t>Reagent Label</t>
+  </si>
+  <si>
+    <t>Name:</t>
   </si>
   <si>
     <t>${name}</t>
@@ -44,37 +44,37 @@
     <t>${basId}</t>
   </si>
   <si>
-    <t>批号:</t>
+    <t>LOT:</t>
   </si>
   <si>
     <t>${batchNo}</t>
   </si>
   <si>
-    <t>存储条件:</t>
+    <t>Storage condition(unopen):</t>
   </si>
   <si>
     <t>${storageCondition}</t>
   </si>
   <si>
-    <t>过期日期:</t>
+    <t>Received date:</t>
+  </si>
+  <si>
+    <t>${receiveDate}</t>
+  </si>
+  <si>
+    <t>Received by:</t>
+  </si>
+  <si>
+    <t>${receiverName}</t>
+  </si>
+  <si>
+    <t>Exp.Date(unopen):</t>
   </si>
   <si>
     <t>${expireDate}</t>
   </si>
   <si>
-    <t>接收人:</t>
-  </si>
-  <si>
-    <t>${receiverName}</t>
-  </si>
-  <si>
-    <t>接收日期:</t>
-  </si>
-  <si>
-    <t>${receiveDate}</t>
-  </si>
-  <si>
-    <t>备注:</t>
+    <t>Remark:</t>
   </si>
   <si>
     <t>${remark}</t>
@@ -173,8 +173,8 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="17.578125" customWidth="true"/>
-    <col min="2" max="2" width="42.96875" customWidth="true"/>
+    <col min="1" max="1" width="27.34375" customWidth="true"/>
+    <col min="2" max="2" width="46.875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
